--- a/data/trans_orig/IP31KM05_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM05_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>104658</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>95160</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>111226</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>85,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>77,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>90,5%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>86034</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>78466</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>93845</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>75,3%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>68,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>116611</t>
+          <t>89109</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106124</t>
+          <t>80271</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>124514</t>
+          <t>96727</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>202645</t>
+          <t>193767</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>191083</t>
+          <t>181275</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>213655</t>
+          <t>204017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18238</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11670</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27736</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>22,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>28217</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20406</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>35785</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>24,7%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>31,32%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20204</t>
+          <t>29489</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>21871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30691</t>
+          <t>38327</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>48421</t>
+          <t>47727</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>37477</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59983</t>
+          <t>60219</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>202200</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>192083</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>210060</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>87,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>83,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>90,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>158740</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>149284</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>166220</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>85,29%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>80,21%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>89,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>214390</t>
+          <t>153928</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>204475</t>
+          <t>145447</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>223970</t>
+          <t>161500</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>373130</t>
+          <t>356127</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>359829</t>
+          <t>341358</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>384952</t>
+          <t>365858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,84%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29041</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21181</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>39158</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>12,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>27374</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19894</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>36830</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,71%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>33130</t>
+          <t>26665</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23550</t>
+          <t>19093</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43045</t>
+          <t>35146</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>60504</t>
+          <t>55706</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48682</t>
+          <t>45975</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73805</t>
+          <t>70475</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>121995</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>110582</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>130855</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>66,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78,58%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>141817</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>127546</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>159742</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>75,33%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>67,75%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>132228</t>
+          <t>113700</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119405</t>
+          <t>103812</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142950</t>
+          <t>122356</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>274046</t>
+          <t>235695</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>254752</t>
+          <t>220777</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297395</t>
+          <t>249904</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>44527</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>35667</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>55940</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>21,42%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>33,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>46432</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>28507</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>60703</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>24,67%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,14%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>32,25%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50861</t>
+          <t>41338</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40139</t>
+          <t>32682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63684</t>
+          <t>51226</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>97293</t>
+          <t>85865</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73944</t>
+          <t>71656</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116587</t>
+          <t>100783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>137157</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>127969</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>145469</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>82,54%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>77,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>87,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>139686</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>130172</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>146262</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>84,91%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>79,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>88,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>145531</t>
+          <t>138618</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>134057</t>
+          <t>128950</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>154147</t>
+          <t>146084</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>285217</t>
+          <t>275775</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>271283</t>
+          <t>264003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>296714</t>
+          <t>286661</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29008</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20696</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38196</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17,46%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>22,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>24833</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18257</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>34347</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15,09%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>31778</t>
+          <t>25361</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23162</t>
+          <t>17895</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43252</t>
+          <t>35029</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>56611</t>
+          <t>54369</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45114</t>
+          <t>43483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70545</t>
+          <t>66141</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>566010</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>547310</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>583530</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>82,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>79,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>84,96%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>734</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>526278</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>506008</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>547004</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>80,58%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>77,47%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>83,75%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>608760</t>
+          <t>495355</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>584740</t>
+          <t>478057</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>626642</t>
+          <t>510739</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1135038</t>
+          <t>1061364</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1105313</t>
+          <t>1036479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1163495</t>
+          <t>1086227</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>120814</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>103294</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>139514</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>17,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>126856</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>106130</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>147126</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>19,42%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>16,25%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>22,53%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>135973</t>
+          <t>122853</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118091</t>
+          <t>107469</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159993</t>
+          <t>140151</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,22 +2280,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>262829</t>
+          <t>243667</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>234372</t>
+          <t>218804</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>292554</t>
+          <t>268552</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
